--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484592_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484592_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7407</v>
+        <v>6.0838</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6603</v>
+        <v>6.2511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0804</v>
+        <v>-0.1673</v>
       </c>
       <c r="G2" t="n">
         <v>2.028</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1644</v>
+        <v>0.1787</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6621</v>
+        <v>-0.0712</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4977</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
         <v>0.945</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6724</v>
+        <v>2.8835</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6242</v>
+        <v>3.1574</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0482</v>
+        <v>-0.2739</v>
       </c>
       <c r="G3" t="n">
         <v>0.5778</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2883</v>
+        <v>0.4994</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4563</v>
+        <v>-0.0105</v>
       </c>
       <c r="U3" t="n">
-        <v>0.832</v>
+        <v>0.51</v>
       </c>
       <c r="V3" t="n">
         <v>1.2566</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2911</v>
+        <v>2.4996</v>
       </c>
       <c r="E4" t="n">
-        <v>2.428</v>
+        <v>1.7688</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1369</v>
+        <v>0.7308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9088000000000001</v>
+        <v>1.1685</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6943</v>
+        <v>2.1079</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7854</v>
+        <v>-0.9394</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8051</v>
+        <v>2.4634</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2695</v>
+        <v>2.9536</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4645</v>
+        <v>-0.4902</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8962</v>
+        <v>-1.2949</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5753</v>
+        <v>-0.8457</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.321</v>
+        <v>-0.4492</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7488</v>
+        <v>-0.8522</v>
       </c>
       <c r="T4" t="n">
-        <v>0.822</v>
+        <v>-0.451</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0732</v>
+        <v>-0.4012</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6335</v>
+        <v>1.5889</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5153</v>
+        <v>1.8855</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0817</v>
+        <v>2.3436</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4335</v>
+        <v>-0.458</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1685</v>
+        <v>2.928</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1079</v>
+        <v>1.5334</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9394</v>
+        <v>1.3946</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4634</v>
+        <v>4.896</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9536</v>
+        <v>2.2509</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4902</v>
+        <v>2.6452</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2949</v>
+        <v>-1.968</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8457</v>
+        <v>-0.7175</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4492</v>
+        <v>-1.2505</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
         <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8365</v>
+        <v>-0.3986</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.138</v>
+        <v>-0.1255</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6985</v>
+        <v>-0.273</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.382</v>
+        <v>1.794</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1373</v>
+        <v>1.9061</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7553</v>
+        <v>-0.1121</v>
       </c>
       <c r="G6" t="n">
-        <v>2.928</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5334</v>
+        <v>1.6943</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3946</v>
+        <v>-0.7854</v>
       </c>
       <c r="J6" t="n">
-        <v>4.896</v>
+        <v>2.8051</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2509</v>
+        <v>3.2695</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6452</v>
+        <v>-0.4645</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.968</v>
+        <v>-1.8962</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7175</v>
+        <v>-1.5753</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2505</v>
+        <v>-0.321</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7489</v>
+        <v>1.8326</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9021</v>
+        <v>0.2517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3318</v>
+        <v>0.3002</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5703</v>
+        <v>-0.0485</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6439</v>
+        <v>0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2719</v>
+        <v>-0.6069</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4342</v>
+        <v>1.0496</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7061</v>
+        <v>-1.6565</v>
       </c>
       <c r="G7" t="n">
         <v>0.1015</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4539</v>
+        <v>0.1188</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7315</v>
+        <v>0.3469</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2777</v>
+        <v>-0.2281</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6439</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7982</v>
+        <v>-0.6171</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4184</v>
+        <v>-0.9648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6202</v>
+        <v>0.3477</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0883</v>
@@ -1078,13 +1078,13 @@
         <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5474</v>
+        <v>-0.3663</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4419</v>
+        <v>0.0117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1055</v>
+        <v>-0.378</v>
       </c>
       <c r="V8" t="n">
         <v>1.2878</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9654</v>
+        <v>-0.8855</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7212</v>
+        <v>-0.6661</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2442</v>
+        <v>-0.2194</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4767</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5333</v>
+        <v>-0.4534</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.522</v>
+        <v>-1.2554</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3442</v>
+        <v>-1.1519</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1778</v>
+        <v>-0.1034</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8934</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.372</v>
+        <v>-0.1054</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>0.0272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0484</v>
+        <v>-4.9602</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3786</v>
+        <v>-3.3647</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6698</v>
+        <v>-1.5955</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5293</v>
@@ -1312,13 +1312,13 @@
         <v>2.7489</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1526</v>
+        <v>-0.0643</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4193</v>
+        <v>0.4333</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5719</v>
+        <v>-0.4976</v>
       </c>
       <c r="V11" t="n">
         <v>0.6335</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.995599999999999</v>
+        <v>6.821299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.503300000000001</v>
+        <v>10.3291</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5078</v>
+        <v>-3.5076</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2751</v>
+        <v>-1.275100000000001</v>
       </c>
       <c r="H12" t="n">
         <v>4.3348</v>
@@ -1369,7 +1369,7 @@
         <v>14.6689</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4833999999999996</v>
+        <v>0.4833999999999987</v>
       </c>
       <c r="M12" t="n">
         <v>-16.4277</v>
@@ -1378,7 +1378,7 @@
         <v>-10.3343</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.093500000000001</v>
+        <v>-6.0935</v>
       </c>
       <c r="P12" t="n">
         <v>5.4977</v>
@@ -1390,13 +1390,13 @@
         <v>18.3258</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0173</v>
+        <v>-1.1916</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4751</v>
+        <v>0.351</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5424</v>
+        <v>-1.5422</v>
       </c>
       <c r="V12" t="n">
         <v>3.7906</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2014</v>
+        <v>2.7579</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1315</v>
+        <v>5.7085</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9301</v>
+        <v>-2.9506</v>
       </c>
       <c r="G13" t="n">
         <v>0.0796</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6662</v>
+        <v>-0.1097</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8265</v>
+        <v>-0.2496</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1603</v>
+        <v>0.1399</v>
       </c>
       <c r="V13" t="n">
         <v>0.9554</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2968</v>
+        <v>1.0824</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9952</v>
+        <v>-0.4097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3016</v>
+        <v>1.4921</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9452</v>
+        <v>-0.0035</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1891</v>
+        <v>0.2112</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2439</v>
+        <v>-0.2147</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9499</v>
+        <v>-0.556</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0653</v>
+        <v>0.0433</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1154</v>
+        <v>-0.5994</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0047</v>
+        <v>0.5525</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8762</v>
+        <v>0.1679</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1285</v>
+        <v>0.3846</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9014</v>
+        <v>0.0963</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8778</v>
+        <v>0.1463</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0235</v>
+        <v>-0.05</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>F. RODRIGUEZ GORDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,37 +1579,37 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9585</v>
+        <v>0.8336</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4097</v>
+        <v>-0.0174</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3682</v>
+        <v>0.8509</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0035</v>
+        <v>0.4028</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2112</v>
+        <v>-0.0235</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2147</v>
+        <v>0.4263</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.556</v>
+        <v>0.1067</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0433</v>
+        <v>0.065</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5994</v>
+        <v>0.0417</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5525</v>
+        <v>0.2961</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1679</v>
+        <v>-0.0885</v>
       </c>
       <c r="O15" t="n">
         <v>0.3846</v>
@@ -1624,28 +1624,28 @@
         <v>0.3665</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0275</v>
+        <v>0.0643</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1463</v>
+        <v>-0.1241</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1738</v>
+        <v>0.1883</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. RODRIGUEZ GORDO</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.6704</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1135</v>
+        <v>0.4183</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0243</v>
+        <v>0.2521</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4028</v>
+        <v>0.9452</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0235</v>
+        <v>2.1891</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4263</v>
+        <v>-1.2439</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1067</v>
+        <v>1.9499</v>
       </c>
       <c r="K16" t="n">
-        <v>0.065</v>
+        <v>3.0653</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0417</v>
+        <v>-1.1154</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2961</v>
+        <v>-1.0047</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0885</v>
+        <v>-0.8762</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3846</v>
+        <v>-0.1285</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1415</v>
+        <v>0.2749</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2202</v>
+        <v>0.3009</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3618</v>
+        <v>-0.026</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3205</v>
+        <v>0.2884</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2561</v>
+        <v>0.2247</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0644</v>
+        <v>0.0638</v>
       </c>
       <c r="G17" t="n">
         <v>0.0167</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2926</v>
+        <v>0.3164</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3303</v>
+        <v>0.1505</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0377</v>
+        <v>0.1659</v>
       </c>
       <c r="V17" t="n">
         <v>0.3219</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4521</v>
+        <v>-0.0893</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.64</v>
+        <v>-0.3516</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1879</v>
+        <v>0.2622</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6744</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1888</v>
+        <v>0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.184</v>
+        <v>0.1045</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0048</v>
+        <v>0.0696</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5619</v>
+        <v>-1.2291</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5881</v>
+        <v>-0.2773</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.15</v>
+        <v>-0.9518</v>
       </c>
       <c r="G19" t="n">
         <v>0.5375</v>
@@ -1936,13 +1936,13 @@
         <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4504</v>
+        <v>0.7832</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4623</v>
+        <v>0.5969</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0119</v>
+        <v>0.1862</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CARRERAS GARRIGA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.751</v>
+        <v>-1.4323</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0722</v>
+        <v>-0.6727</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8232</v>
+        <v>-0.7595</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3277</v>
+        <v>-0.8003</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4768</v>
+        <v>-0.4736</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8045</v>
+        <v>-0.3267</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0986</v>
+        <v>1.0317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3901</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7085</v>
+        <v>0.1864</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7709</v>
+        <v>-1.832</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.867</v>
+        <v>-1.3189</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0961</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2619</v>
+        <v>0.1011</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1101</v>
+        <v>-0.0105</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1518</v>
+        <v>0.1116</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. CARRERAS GARRIGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1374</v>
+        <v>-1.4523</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2497</v>
+        <v>0.1684</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8877</v>
+        <v>-1.6206</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8003</v>
+        <v>0.3277</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4736</v>
+        <v>-0.4768</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3267</v>
+        <v>0.8045</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0317</v>
+        <v>1.0986</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.3901</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1864</v>
+        <v>0.7085</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.832</v>
+        <v>-0.7709</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3189</v>
+        <v>-0.867</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>0.0961</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6041</v>
+        <v>0.0368</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5875</v>
+        <v>-0.0139</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0166</v>
+        <v>0.0507</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1387</v>
+        <v>-1.8459</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8142</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3246</v>
+        <v>-1.3202</v>
       </c>
       <c r="G22" t="n">
         <v>3.6812</v>
@@ -2170,13 +2170,13 @@
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0449</v>
+        <v>0.2479</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2217</v>
+        <v>0.0668</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1768</v>
+        <v>0.1812</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6439</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0016</v>
+        <v>-4.9384</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2039</v>
+        <v>-0.7577</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2055</v>
+        <v>-4.1807</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2372</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>1.61</v>
+        <v>0.6733</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5362</v>
+        <v>0.5747</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0738</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1912</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.995699999999999</v>
+        <v>-5.3546</v>
       </c>
       <c r="E24" t="n">
-        <v>3.507699999999999</v>
+        <v>3.5078</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.503499999999999</v>
+        <v>-8.862300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>1.2753</v>
@@ -2326,13 +2326,13 @@
         <v>12.828</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0173</v>
+        <v>2.6585</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5423</v>
+        <v>1.5425</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4750000000000001</v>
+        <v>1.116</v>
       </c>
       <c r="V24" t="n">
         <v>-3.7906</v>
@@ -2341,7 +2341,7 @@
         <v>3.8633</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.6538</v>
+        <v>-7.653799999999999</v>
       </c>
     </row>
   </sheetData>
